--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Work\Quick Access\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7643FB8D-F96D-46AD-A3A0-CDBF5EED982B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11791809-A83C-402C-9673-C82CE559E572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="325">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1008,6 +1008,15 @@
   </si>
   <si>
     <t>public decimal MaxQty { get; set; }</t>
+  </si>
+  <si>
+    <t>Default H columns</t>
+  </si>
+  <si>
+    <t>Default I columns</t>
+  </si>
+  <si>
+    <t>SR_NO (Composite PK)</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1113,13 +1122,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1455,10 +1460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
-  <dimension ref="A2:G109"/>
+  <dimension ref="A2:G131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.140625" bestFit="1" customWidth="1"/>
@@ -1470,13 +1475,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2100,7 +2105,7 @@
       <c r="A39" s="5">
         <v>36</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="11" t="s">
         <v>82</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -2613,7 +2618,7 @@
       <c r="B69" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -2630,7 +2635,7 @@
       <c r="B70" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" t="s">
         <v>168</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -2848,7 +2853,7 @@
       <c r="A83" s="5">
         <v>80</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="12" t="s">
         <v>259</v>
       </c>
       <c r="C83" s="3" t="s">
@@ -2987,7 +2992,7 @@
       <c r="B91" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" t="s">
         <v>168</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -3155,14 +3160,272 @@
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B115" s="13"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
+        <v>1</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="5">
+        <v>2</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="5">
+        <v>3</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="5">
+        <v>4</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
+        <v>5</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
+        <v>6</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
+        <v>7</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
+        <v>8</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B126" s="13"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="5">
+        <v>1</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
+        <v>2</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="5">
+        <v>3</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
+        <v>4</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B3:E3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E103">
       <sortCondition ref="B3"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A126:E126"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3204,15 +3467,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11791809-A83C-402C-9673-C82CE559E572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9788D46-4ECB-4E4A-91C7-B4A9DF6EFC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView minimized="1" xWindow="19065" yWindow="3540" windowWidth="9570" windowHeight="11295" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Sorter" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$C$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sorter!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Type Sheet'!$B$3:$E$3</definedName>
   </definedNames>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="385">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1017,6 +1018,186 @@
   </si>
   <si>
     <t>SR_NO (Composite PK)</t>
+  </si>
+  <si>
+    <t>RECOVERY_TYPE</t>
+  </si>
+  <si>
+    <t>UTYPE_Decimal1:decimal(14, 2)</t>
+  </si>
+  <si>
+    <t>INSTALLMENT_AMOUNT</t>
+  </si>
+  <si>
+    <t>public int RECOVERY_TYPE { get; set; }</t>
+  </si>
+  <si>
+    <t>public int RecoveryType  { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal INSTALLMENT_AMOUNT { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal InstallmentAmount { get; set; }</t>
+  </si>
+  <si>
+    <t>CONSUMER_CODE</t>
+  </si>
+  <si>
+    <t>public int CONSUMER_CODE { get; set; }</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>Namespace</t>
+  </si>
+  <si>
+    <t>using Dapper;</t>
+  </si>
+  <si>
+    <t>using System;</t>
+  </si>
+  <si>
+    <t>using System.Collections.Generic;</t>
+  </si>
+  <si>
+    <t>using System.Linq;</t>
+  </si>
+  <si>
+    <t>using System.Text;</t>
+  </si>
+  <si>
+    <t>using System.Threading.Tasks;</t>
+  </si>
+  <si>
+    <t>DateUtility</t>
+  </si>
+  <si>
+    <t>using ZanvarGroup.Erp.Business.Base;</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>using System.IO;</t>
+  </si>
+  <si>
+    <t>using System.Net;</t>
+  </si>
+  <si>
+    <t>using Newtonsoft.Json;</t>
+  </si>
+  <si>
+    <t>using System.Transactions;</t>
+  </si>
+  <si>
+    <t>using System.Configuration;</t>
+  </si>
+  <si>
+    <t>SrNo</t>
+  </si>
+  <si>
+    <t>SELLER_COMPANY_CODE</t>
+  </si>
+  <si>
+    <t>CUSTOMER_CODE</t>
+  </si>
+  <si>
+    <t>public int ConsumerCode { get; set; }</t>
+  </si>
+  <si>
+    <t>public int CUSTOMER_CODE { get; set; }</t>
+  </si>
+  <si>
+    <t>public int CustomerCode { get; set; }</t>
+  </si>
+  <si>
+    <t>public int SELLER_COMPANY_CODE { get; set; }</t>
+  </si>
+  <si>
+    <t>public int SellerCompanyCode { get; set; }</t>
+  </si>
+  <si>
+    <t>PACKING_DESTINATION</t>
+  </si>
+  <si>
+    <t>public int PACKING_DESTINATION { get; set; }</t>
+  </si>
+  <si>
+    <t>public int PackingDestination { get; set; }</t>
+  </si>
+  <si>
+    <t>IS_PRICE_BREAKUP_AVAILABLE</t>
+  </si>
+  <si>
+    <t>public int IS_PRICE_BREAKUP_AVAILABLE { get; set; }</t>
+  </si>
+  <si>
+    <t>public int IsPriceBreakupAvailable { get; set; }</t>
+  </si>
+  <si>
+    <t>EFFECTIVE_FROM</t>
+  </si>
+  <si>
+    <t>public string EFFECTIVE_FROM { get; set; }</t>
+  </si>
+  <si>
+    <t>public string EffectiveDate { get; set; }</t>
+  </si>
+  <si>
+    <t>PER_BOX_QTY</t>
+  </si>
+  <si>
+    <t>public int PER_BOX_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public int PerBoxQty { get; set; }</t>
+  </si>
+  <si>
+    <t>PER_BOX_PART_QTY</t>
+  </si>
+  <si>
+    <t>public int PER_BOX_PART_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public int PerBoxPartQty { get; set; }</t>
+  </si>
+  <si>
+    <t>using ZanvarGroup.Erp.DTO.Configs.Interfaces;</t>
+  </si>
+  <si>
+    <t>ICnfTranTypes</t>
+  </si>
+  <si>
+    <t>using ZanvarGroup.Erp.DALDapper.Implementation.Configs;</t>
+  </si>
+  <si>
+    <t>DALCnfTranTypes</t>
+  </si>
+  <si>
+    <t>AccountSubGlEntity</t>
+  </si>
+  <si>
+    <t>AccountSubGlService</t>
+  </si>
+  <si>
+    <t>CustomerAccountEntity</t>
+  </si>
+  <si>
+    <t>CustomerAccountService</t>
+  </si>
+  <si>
+    <t>StockGroup</t>
+  </si>
+  <si>
+    <t>MaterialsEntity</t>
+  </si>
+  <si>
+    <t>MaterialsService</t>
+  </si>
+  <si>
+    <t>TransactionScope</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1119,9 +1300,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1464,7 +1642,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.7109375" bestFit="1" customWidth="1"/>
@@ -1475,13 +1653,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1715,16 +1893,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1732,16 +1910,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1749,16 +1927,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1766,16 +1944,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1783,16 +1961,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1800,16 +1978,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>131</v>
+        <v>43</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1817,16 +1995,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1834,16 +2012,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1851,16 +2029,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1868,16 +2046,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,50 +2063,50 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>249</v>
+        <v>364</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>251</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>24</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>55</v>
+      <c r="B27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>58</v>
+      <c r="B28" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>206</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,16 +2114,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,33 +2131,33 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>54</v>
+        <v>30</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>28</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>246</v>
+      <c r="B31" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>247</v>
+        <v>57</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>248</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1987,33 +2165,33 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>30</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>262</v>
+      <c r="B33" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>263</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2021,16 +2199,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2038,16 +2216,16 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>85</v>
+        <v>243</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>91</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2055,16 +2233,16 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2072,16 +2250,16 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>18</v>
+        <v>327</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>46</v>
+        <v>330</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>81</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2089,33 +2267,33 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>245</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>36</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>82</v>
+      <c r="B39" t="s">
+        <v>361</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>86</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2123,16 +2301,16 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2140,16 +2318,16 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2157,16 +2335,16 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>198</v>
+        <v>46</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2174,33 +2352,33 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>64</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>41</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>286</v>
+      <c r="B44" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>296</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2208,16 +2386,16 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>300</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2225,16 +2403,16 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2242,16 +2420,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>282</v>
+        <v>198</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2259,16 +2437,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>278</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2276,16 +2454,16 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>122</v>
+        <v>286</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>125</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2293,33 +2471,33 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>239</v>
+        <v>292</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>27</v>
+      <c r="B51" s="3" t="s">
+        <v>319</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>52</v>
+        <v>317</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>73</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2327,16 +2505,16 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>32</v>
+        <v>275</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2344,16 +2522,16 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>32</v>
+        <v>279</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2361,16 +2539,16 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>135</v>
+        <v>274</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>136</v>
+        <v>281</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>137</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2378,16 +2556,16 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2395,16 +2573,16 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>90</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2412,33 +2590,33 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>55</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>214</v>
+      <c r="B58" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>222</v>
+        <v>52</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2446,16 +2624,16 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>141</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2463,16 +2641,16 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>123</v>
+        <v>304</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2480,16 +2658,16 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>123</v>
+        <v>301</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2497,16 +2675,16 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2514,16 +2692,16 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>190</v>
+        <v>370</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2531,33 +2709,33 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>132</v>
+        <v>367</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>133</v>
+        <v>368</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>134</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>62</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>28</v>
+      <c r="B65" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>74</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2565,33 +2743,33 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>64</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>26</v>
+      <c r="B67" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2599,16 +2777,16 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2616,16 +2794,16 @@
         <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2633,16 +2811,16 @@
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>167</v>
+        <v>268</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2650,16 +2828,16 @@
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2667,16 +2845,16 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2684,16 +2862,16 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2701,16 +2879,16 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>233</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2718,33 +2896,33 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>50</v>
+        <v>328</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>71</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>73</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>149</v>
+      <c r="B76" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2752,33 +2930,33 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>75</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>179</v>
+      <c r="B78" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>193</v>
+        <v>51</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2786,16 +2964,16 @@
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2803,16 +2981,16 @@
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2820,16 +2998,16 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2837,33 +3015,33 @@
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>219</v>
+        <v>166</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>234</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>80</v>
       </c>
-      <c r="B83" s="12" t="s">
-        <v>259</v>
+      <c r="B83" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2871,16 +3049,16 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>17</v>
+        <v>351</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2888,33 +3066,33 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>83</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>56</v>
+      <c r="B86" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2922,16 +3100,16 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2939,16 +3117,16 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>79</v>
+        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2956,16 +3134,16 @@
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2973,16 +3151,16 @@
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2990,16 +3168,16 @@
         <v>88</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="C91" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>316</v>
+        <v>188</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3007,107 +3185,187 @@
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>319</v>
+        <v>9</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>321</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>90</v>
       </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
+      <c r="B93" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>91</v>
       </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
+      <c r="B94" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>92</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
+      <c r="B95" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>93</v>
       </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
+      <c r="B96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>94</v>
       </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
+      <c r="B97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>95</v>
       </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
+      <c r="B98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>96</v>
       </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
+      <c r="B99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>97</v>
       </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
+      <c r="B100" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>98</v>
       </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
+      <c r="B101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>99</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
+      <c r="B102" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
@@ -3161,13 +3419,13 @@
       <c r="E109" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="B115" s="13"/>
-      <c r="C115" s="13"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -3323,13 +3581,13 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
@@ -3434,21 +3692,323 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FBB90E-FF6B-41AA-ABD7-678833F5A1B7}">
-  <dimension ref="A3:A19"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G7" s="5">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G8" s="5">
+        <v>6</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="5">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="5">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G11" s="5">
+        <v>9</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G13" s="5">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="5">
+        <v>12</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="5">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="5">
+        <v>14</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G17" s="5">
+        <v>15</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="5">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="C2:D2" xr:uid="{E2FBB90E-FF6B-41AA-ABD7-678833F5A1B7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:D13">
+      <sortCondition ref="C2"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3467,15 +4027,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9788D46-4ECB-4E4A-91C7-B4A9DF6EFC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336301C4-4F0D-4961-81C2-7169BFF2F25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="19065" yWindow="3540" windowWidth="9570" windowHeight="11295" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Sources" sheetId="3" r:id="rId2"/>
     <sheet name="Sorter" sheetId="2" r:id="rId3"/>
+    <sheet name="Implementation" sheetId="4" r:id="rId4"/>
+    <sheet name="Script making" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$C$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sorter!$B$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sources!$C$2:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Type Sheet'!$B$3:$E$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="437">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1198,6 +1200,162 @@
   </si>
   <si>
     <t>TransactionScope</t>
+  </si>
+  <si>
+    <t>Saving Default Sources</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Excess</t>
+  </si>
+  <si>
+    <t>Int64 intTrnNo = 0; if (_dtoCnfTranTypes != null) { intTrnNo = _dalPdH.GetTranNo(TranType, _dtoCnfTranTypes.TRAN_SERIES, strFinancialYear); if (intTrnNo == 1) { intTrnNo = CustomTranNo.GetCustomTranNo(TranType, _dtoCnfTranTypes.TRAN_SERIES, strTranDate); } } bObj.TrnNo = intTrnNo;</t>
+  </si>
+  <si>
+    <t>string strTranDate = DateUtility.getFormatedDate(bObj.TrnDate, 1); bObj.TrnDate = strTranDate;</t>
+  </si>
+  <si>
+    <t>public static int TranSubType = 10; bObj.TrnSubType = TranSubType;</t>
+  </si>
+  <si>
+    <t>MstMenu _objMstMenu = MstMenu.getMenuById(MenuId); bObj.DocType = _objMstMenu.VouType;</t>
+  </si>
+  <si>
+    <t>AMEND_NO (Create)</t>
+  </si>
+  <si>
+    <t>bObj.AmendNo = 0;</t>
+  </si>
+  <si>
+    <t>int intStatusCode = 0; if (Convert.ToBoolean(_objMstMenu.ApprovalReq) == true) { intStatusCode = 101; } bObj.StatusCode = intStatusCode;</t>
+  </si>
+  <si>
+    <t>STATUS_CODE (Create)</t>
+  </si>
+  <si>
+    <t>Menu Script</t>
+  </si>
+  <si>
+    <t>[MENU_ID]</t>
+  </si>
+  <si>
+    <t>[MENU_SHORT_NAME]</t>
+  </si>
+  <si>
+    <t>BRDEPMM</t>
+  </si>
+  <si>
+    <t>[MENU_NAME]</t>
+  </si>
+  <si>
+    <t>BRANCH DEPARTMENT WISE MIN MAX</t>
+  </si>
+  <si>
+    <t>[MENU_DOC_NO]</t>
+  </si>
+  <si>
+    <t>[CONSOLE_URL]</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>[PAGE_URL]</t>
+  </si>
+  <si>
+    <t>[VIEW_PAGE]</t>
+  </si>
+  <si>
+    <t>[PRINT_URL]</t>
+  </si>
+  <si>
+    <t>[CONCATE_URL]</t>
+  </si>
+  <si>
+    <t>[SEQUENCE]</t>
+  </si>
+  <si>
+    <t>[MENU_DESCRIPTION]</t>
+  </si>
+  <si>
+    <t>[ALLOW_PAGING]</t>
+  </si>
+  <si>
+    <t>[PAGE_RECORDS]</t>
+  </si>
+  <si>
+    <t>[ENTRY_DAYS]</t>
+  </si>
+  <si>
+    <t>[VIEW_DAYS]</t>
+  </si>
+  <si>
+    <t>[PARENT_MENU_ID]</t>
+  </si>
+  <si>
+    <t>[APPROVAL_REQ]</t>
+  </si>
+  <si>
+    <t>[APPROVAL_LEVEL]</t>
+  </si>
+  <si>
+    <t>[IS_TYPEWS_NO]</t>
+  </si>
+  <si>
+    <t>[IS_MONTHLY_NO]</t>
+  </si>
+  <si>
+    <t>[VOU_TYPE]</t>
+  </si>
+  <si>
+    <t>[REPORT_NAME]</t>
+  </si>
+  <si>
+    <t>DMP</t>
+  </si>
+  <si>
+    <t>[CRT_BY]</t>
+  </si>
+  <si>
+    <t>[STATUS_CODE]</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>[SYS_LOGIN]</t>
+  </si>
+  <si>
+    <t>[SYS_DATE_TIME]</t>
+  </si>
+  <si>
+    <t>[MENU_IMG]</t>
+  </si>
+  <si>
+    <t>[MODULE_ID]</t>
+  </si>
+  <si>
+    <t>[IS_MOB_APP]</t>
+  </si>
+  <si>
+    <t>[ICON]</t>
+  </si>
+  <si>
+    <t>[STATE]</t>
+  </si>
+  <si>
+    <t>[IS_GROUP]</t>
+  </si>
+  <si>
+    <t>[TRN_MODULE_ID]</t>
+  </si>
+  <si>
+    <t>LastPurchaseRate</t>
+  </si>
+  <si>
+    <t>using ZanvarGroup.Erp.Business.Queries;</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1301,8 +1459,26 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1653,13 +1829,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3419,13 +3595,13 @@
       <c r="E109" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12"/>
-      <c r="E115" s="12"/>
+      <c r="B115" s="17"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="17"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -3581,13 +3757,13 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="B126" s="12"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="12"/>
-      <c r="E126" s="12"/>
+      <c r="B126" s="17"/>
+      <c r="C126" s="17"/>
+      <c r="D126" s="17"/>
+      <c r="E126" s="17"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
@@ -3944,6 +4120,15 @@
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>436</v>
+      </c>
       <c r="G14" s="5">
         <v>12</v>
       </c>
@@ -4027,15 +4212,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
@@ -4363,4 +4548,650 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{848ABD2B-D78F-4FB4-B4A9-ED110CEE9F34}">
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="18" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="2:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C088354-24CD-486E-BF8F-F5E1CEBCD84D}">
+  <dimension ref="C2:J35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="H2" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E3" s="13">
+        <v>40200</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J3" s="13">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C5" s="3">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" s="13">
+        <v>40200</v>
+      </c>
+      <c r="H6" s="3">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J6" s="13">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="3">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="J7" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H8" s="3">
+        <v>6</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="J8" s="13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C9" s="3">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H9" s="3">
+        <v>7</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J9" s="13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="3">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H10" s="3">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J10" s="13">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C11" s="3">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H11" s="3">
+        <v>9</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J11" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C12" s="3">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C13" s="3">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="H13" s="3">
+        <v>11</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C14" s="3">
+        <v>12</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="3">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="13">
+        <v>60</v>
+      </c>
+      <c r="H15" s="3">
+        <v>13</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C16" s="3">
+        <v>14</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="J16" s="15">
+        <v>43572.553746678241</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C17" s="3">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E17" s="13">
+        <v>60</v>
+      </c>
+      <c r="H17" s="3">
+        <v>15</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="J17" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C18" s="3">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E18" s="13">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C19" s="3">
+        <v>17</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E19" s="13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C20" s="3">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="3">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C22" s="3">
+        <v>20</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C23" s="3">
+        <v>21</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="3">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="3">
+        <v>23</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C26" s="3">
+        <v>24</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C27" s="3">
+        <v>25</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C28" s="3">
+        <v>26</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E28" s="14">
+        <v>43572</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C29" s="3">
+        <v>27</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0.55374667824074075</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C30" s="3">
+        <v>28</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C31" s="3">
+        <v>29</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E31" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C32" s="3">
+        <v>30</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="3">
+        <v>31</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="3">
+        <v>32</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="3">
+        <v>33</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="H2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336301C4-4F0D-4961-81C2-7169BFF2F25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>
@@ -1471,10 +1471,10 @@
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1829,13 +1829,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3595,13 +3595,13 @@
       <c r="E109" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="17"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -3757,13 +3757,13 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B126" s="17"/>
-      <c r="C126" s="17"/>
-      <c r="D126" s="17"/>
-      <c r="E126" s="17"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
@@ -4212,15 +4212,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
@@ -4562,11 +4562,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="18" t="s">
         <v>387</v>
       </c>
@@ -4677,16 +4677,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="H2" s="16" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="H2" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
     </row>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" s="3">

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336301C4-4F0D-4961-81C2-7169BFF2F25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5395B5E-C849-4CBE-842F-6FC16DC04B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="442">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -947,9 +947,6 @@
     <t>to formatted Trn in BO use string</t>
   </si>
   <si>
-    <t>public decimal MaterialWeight { get; set; }</t>
-  </si>
-  <si>
     <t>PARTY_BILL_NO</t>
   </si>
   <si>
@@ -1356,6 +1353,24 @@
   </si>
   <si>
     <t>using ZanvarGroup.Erp.Business.Queries;</t>
+  </si>
+  <si>
+    <t>SUPPLIER_PERCENTAGE</t>
+  </si>
+  <si>
+    <t>BOM_TYPE</t>
+  </si>
+  <si>
+    <t>public int BOM_TYPE { get; set; }</t>
+  </si>
+  <si>
+    <t>public int BomType { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal SUPPLIER_PERCENTAGE { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal SupplierPercentage{ get; set; }</t>
   </si>
 </sst>
 </file>
@@ -1876,16 +1891,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1950,16 +1965,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>252</v>
+        <v>437</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>253</v>
+        <v>438</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>254</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1967,16 +1982,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1984,16 +1999,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>144</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,16 +2016,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2018,16 +2033,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2035,16 +2050,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>87</v>
+        <v>44</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2052,16 +2067,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>175</v>
+        <v>45</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2069,16 +2084,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>332</v>
+        <v>174</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>333</v>
+        <v>176</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>353</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2086,16 +2101,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2103,16 +2118,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2120,16 +2135,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2137,16 +2152,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2154,16 +2169,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2171,16 +2186,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>352</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>355</v>
+        <v>43</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2188,16 +2203,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>351</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>130</v>
+        <v>353</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>131</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2205,16 +2220,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>310</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>311</v>
+        <v>130</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>312</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2222,16 +2237,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>309</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>310</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>62</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2239,16 +2254,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>364</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>365</v>
+        <v>38</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>366</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2256,16 +2271,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>216</v>
+        <v>363</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>221</v>
+        <v>364</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>228</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2273,16 +2288,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2290,33 +2305,33 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>55</v>
+      <c r="B30" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2324,67 +2339,67 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>57</v>
+        <v>30</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>29</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>283</v>
+      <c r="B32" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>291</v>
+        <v>57</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>295</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>29</v>
+      <c r="B33" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>75</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>246</v>
+      <c r="B34" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>247</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>248</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2392,16 +2407,16 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2409,16 +2424,16 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2426,16 +2441,16 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>326</v>
+        <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>330</v>
+        <v>263</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2443,16 +2458,16 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>181</v>
+        <v>326</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>182</v>
+        <v>329</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>183</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2460,16 +2475,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>361</v>
+        <v>181</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>362</v>
+        <v>182</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>363</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2477,16 +2492,16 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>85</v>
+        <v>361</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>91</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2494,16 +2509,16 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>197</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2511,16 +2526,16 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2528,50 +2543,50 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>41</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>82</v>
+      <c r="B44" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>86</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>42</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>184</v>
+      <c r="B45" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2579,16 +2594,16 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>256</v>
+        <v>184</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>257</v>
+        <v>185</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>258</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2596,16 +2611,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2613,16 +2628,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2630,16 +2645,16 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>286</v>
+        <v>8</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>292</v>
+        <v>40</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>296</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2650,13 +2665,13 @@
         <v>286</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>292</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2664,16 +2679,16 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2749,16 +2764,16 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2800,16 +2815,16 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2817,16 +2832,16 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2834,16 +2849,16 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2868,16 +2883,16 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2885,16 +2900,16 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2905,7 +2920,7 @@
         <v>148</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>151</v>
@@ -2955,7 +2970,7 @@
       <c r="B68" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -2989,7 +3004,7 @@
       <c r="B70" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3072,16 +3087,16 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3190,7 +3205,7 @@
       <c r="A82" s="5">
         <v>79</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="11" t="s">
         <v>166</v>
       </c>
       <c r="C82" s="3" t="s">
@@ -3207,7 +3222,7 @@
       <c r="A83" s="5">
         <v>80</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="3" t="s">
         <v>285</v>
       </c>
       <c r="C83" s="3" t="s">
@@ -3225,16 +3240,16 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3329,7 +3344,7 @@
       <c r="B90" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" t="s">
         <v>180</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -3346,7 +3361,7 @@
       <c r="B91" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
         <v>180</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -3412,16 +3427,16 @@
         <v>92</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>259</v>
+        <v>436</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>87</v>
+        <v>325</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3429,7 +3444,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>13</v>
@@ -3446,10 +3461,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>88</v>
@@ -3462,34 +3477,34 @@
       <c r="A98" s="5">
         <v>95</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>77</v>
+      <c r="B98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>96</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>36</v>
+      <c r="B99" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3497,16 +3512,16 @@
         <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -3514,16 +3529,16 @@
         <v>98</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -3531,26 +3546,34 @@
         <v>99</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>165</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>100</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
+      <c r="B103" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
@@ -3596,7 +3619,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
@@ -3758,7 +3781,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
@@ -3787,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>5</v>
@@ -3852,7 +3875,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B3:E3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E103">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E104">
       <sortCondition ref="B3"/>
     </sortState>
   </autoFilter>
@@ -3881,22 +3904,22 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
@@ -3904,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>146</v>
@@ -3913,10 +3936,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
@@ -3924,7 +3947,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>147</v>
@@ -3933,10 +3956,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
@@ -3944,7 +3967,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>146</v>
@@ -3953,10 +3976,10 @@
         <v>3</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
@@ -3964,7 +3987,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>147</v>
@@ -3973,10 +3996,10 @@
         <v>4</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
@@ -3984,19 +4007,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -4004,19 +4027,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="G8" s="5">
         <v>6</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -4024,19 +4047,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G9" s="5">
         <v>7</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -4044,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>146</v>
@@ -4053,10 +4076,10 @@
         <v>8</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -4064,7 +4087,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>147</v>
@@ -4073,10 +4096,10 @@
         <v>9</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -4084,7 +4107,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>203</v>
@@ -4093,10 +4116,10 @@
         <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -4104,19 +4127,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G13" s="5">
         <v>11</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -4124,19 +4147,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="G14" s="5">
         <v>12</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -4144,10 +4167,10 @@
         <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -4155,10 +4178,10 @@
         <v>14</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -4166,10 +4189,10 @@
         <v>15</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -4177,10 +4200,10 @@
         <v>16</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -4563,23 +4586,23 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E3" s="18"/>
     </row>
@@ -4589,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -4601,10 +4624,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -4613,22 +4636,22 @@
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -4637,22 +4660,22 @@
         <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4678,12 +4701,12 @@
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="H2" s="17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
@@ -4693,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E3" s="13">
         <v>40200</v>
@@ -4702,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J3" s="13">
         <v>40200</v>
@@ -4713,19 +4736,19 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>398</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>399</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J4" s="13" t="s">
         <v>398</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
@@ -4733,19 +4756,19 @@
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>400</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>401</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>400</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
@@ -4753,7 +4776,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E6" s="13">
         <v>40200</v>
@@ -4762,7 +4785,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J6" s="13">
         <v>40200</v>
@@ -4773,16 +4796,16 @@
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>403</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>404</v>
       </c>
       <c r="H7" s="3">
         <v>5</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J7" s="13" t="b">
         <v>1</v>
@@ -4793,16 +4816,16 @@
         <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H8" s="3">
         <v>6</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J8" s="13">
         <v>60</v>
@@ -4813,16 +4836,16 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H9" s="3">
         <v>7</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J9" s="13">
         <v>60</v>
@@ -4833,16 +4856,16 @@
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H10" s="3">
         <v>8</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J10" s="13">
         <v>401</v>
@@ -4853,16 +4876,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H11" s="3">
         <v>9</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J11" s="13" t="b">
         <v>1</v>
@@ -4873,7 +4896,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
@@ -4882,7 +4905,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J12" s="13">
         <v>0</v>
@@ -4893,19 +4916,19 @@
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H13" s="3">
         <v>11</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
@@ -4913,7 +4936,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E14" s="13" t="b">
         <v>1</v>
@@ -4922,7 +4945,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J14" s="13">
         <v>0</v>
@@ -4933,7 +4956,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E15" s="13">
         <v>60</v>
@@ -4942,10 +4965,10 @@
         <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
@@ -4953,7 +4976,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E16" s="13">
         <v>0</v>
@@ -4962,7 +4985,7 @@
         <v>14</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J16" s="15">
         <v>43572.553746678241</v>
@@ -4973,7 +4996,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E17" s="13">
         <v>60</v>
@@ -4982,7 +5005,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J17" s="13">
         <v>4</v>
@@ -4993,7 +5016,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E18" s="13">
         <v>401</v>
@@ -5004,7 +5027,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E19" s="13" t="b">
         <v>1</v>
@@ -5015,7 +5038,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
@@ -5026,10 +5049,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
@@ -5037,10 +5060,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.25">
@@ -5048,10 +5071,10 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
@@ -5059,10 +5082,10 @@
         <v>22</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.25">
@@ -5070,10 +5093,10 @@
         <v>23</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.25">
@@ -5081,7 +5104,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E26" s="13">
         <v>0</v>
@@ -5092,10 +5115,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.25">
@@ -5103,7 +5126,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E28" s="14">
         <v>43572</v>
@@ -5114,7 +5137,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E29" s="15">
         <v>0.55374667824074075</v>
@@ -5125,10 +5148,10 @@
         <v>28</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.25">
@@ -5136,7 +5159,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E31" s="13">
         <v>4</v>
@@ -5147,10 +5170,10 @@
         <v>30</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.25">
@@ -5158,10 +5181,10 @@
         <v>31</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.25">
@@ -5169,10 +5192,10 @@
         <v>32</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.25">
@@ -5180,10 +5203,10 @@
         <v>33</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5395B5E-C849-4CBE-842F-6FC16DC04B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BEFF61-0EB0-438C-A172-2FE4D6625B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="461">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1148,12 +1148,6 @@
     <t>PER_BOX_QTY</t>
   </si>
   <si>
-    <t>public int PER_BOX_QTY { get; set; }</t>
-  </si>
-  <si>
-    <t>public int PerBoxQty { get; set; }</t>
-  </si>
-  <si>
     <t>PER_BOX_PART_QTY</t>
   </si>
   <si>
@@ -1371,6 +1365,69 @@
   </si>
   <si>
     <t>public decimal SupplierPercentage{ get; set; }</t>
+  </si>
+  <si>
+    <t>PER_QTY</t>
+  </si>
+  <si>
+    <t>PRD_QTY</t>
+  </si>
+  <si>
+    <t>public int PRD_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public int PrdQty { get; set; }</t>
+  </si>
+  <si>
+    <t>STANDARD_CON_QTY</t>
+  </si>
+  <si>
+    <t>public int STANDARD_CON_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public int StandartConQty { get; set; }</t>
+  </si>
+  <si>
+    <t>ACTUAL_CON_QTY</t>
+  </si>
+  <si>
+    <t>public int ACTUAL_CON_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public int ActualConQty { get; set; }</t>
+  </si>
+  <si>
+    <t>DIFF_QTY</t>
+  </si>
+  <si>
+    <t>public decimal DIFF_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal DiffQty { get; set; }</t>
+  </si>
+  <si>
+    <t>ConfigurationManager</t>
+  </si>
+  <si>
+    <t>MstMenu</t>
+  </si>
+  <si>
+    <t>DTOCnfTranTypes</t>
+  </si>
+  <si>
+    <t>using ZanvarGroup.Erp.DTO.Configs.Objects;</t>
+  </si>
+  <si>
+    <t>public decimal PER_BOX_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal PER_QTY { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal PerBoxQty { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal PerQty { get; set; }</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1530,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1485,6 +1541,9 @@
     </xf>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1874,16 +1933,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>447</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>448</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>159</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1891,16 +1950,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>312</v>
+        <v>150</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>314</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1908,16 +1967,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>313</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>69</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1925,16 +1984,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
         <v>298</v>
@@ -1945,16 +2004,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
         <v>299</v>
@@ -1965,16 +2024,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>437</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>438</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>439</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1982,16 +2041,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>252</v>
+        <v>435</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>253</v>
+        <v>436</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>254</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,16 +2058,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>308</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2016,16 +2075,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>144</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2033,16 +2092,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,16 +2109,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,16 +2126,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>87</v>
+        <v>44</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2084,16 +2143,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>175</v>
+        <v>45</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,16 +2160,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>332</v>
+        <v>176</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>352</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2118,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2135,16 +2194,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,16 +2211,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,16 +2228,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2245,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>87</v>
+        <v>42</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,16 +2262,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>354</v>
+        <v>43</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2220,16 +2279,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>351</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>130</v>
+        <v>353</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>131</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2237,16 +2296,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>309</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>311</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,16 +2313,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>309</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>38</v>
+        <v>310</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>62</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2271,16 +2330,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>363</v>
+        <v>450</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>364</v>
+        <v>451</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>365</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,16 +2347,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>221</v>
+        <v>38</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>228</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2305,16 +2364,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>205</v>
+        <v>363</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>207</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2322,67 +2381,67 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>55</v>
+      <c r="B31" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>58</v>
+      <c r="B32" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>57</v>
+        <v>250</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>80</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>30</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>291</v>
+      <c r="B33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2390,16 +2449,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2407,33 +2466,33 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>33</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>213</v>
+      <c r="B36" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>243</v>
+        <v>54</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>229</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,16 +2500,16 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,16 +2517,16 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>326</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>325</v>
+        <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>330</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2475,16 +2534,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2492,16 +2551,16 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>5</v>
+        <v>325</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2509,16 +2568,16 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2526,16 +2585,16 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>196</v>
+        <v>361</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>197</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2543,16 +2602,16 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2560,33 +2619,33 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>244</v>
+        <v>196</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>82</v>
+      <c r="B45" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2594,33 +2653,33 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>44</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>256</v>
+      <c r="B47" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2628,16 +2687,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,16 +2704,16 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>8</v>
+        <v>256</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>64</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2662,16 +2721,16 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>292</v>
+        <v>198</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>296</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,16 +2738,16 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>318</v>
+        <v>8</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>320</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2696,16 +2755,16 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2713,16 +2772,16 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2730,16 +2789,16 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2747,16 +2806,16 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>122</v>
+        <v>279</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>124</v>
+        <v>282</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2764,16 +2823,16 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2781,33 +2840,33 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>239</v>
+        <v>124</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>241</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>55</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>27</v>
+      <c r="B58" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>73</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2815,33 +2874,33 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>357</v>
+        <v>237</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>358</v>
+        <v>239</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>359</v>
+        <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>57</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>32</v>
+      <c r="B60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>304</v>
+        <v>52</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>305</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2849,16 +2908,16 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>32</v>
+        <v>357</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2866,16 +2925,16 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>5</v>
+        <v>303</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>136</v>
+        <v>304</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>137</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2883,16 +2942,16 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>5</v>
+        <v>300</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>370</v>
+        <v>301</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>371</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,16 +2959,16 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>366</v>
+        <v>135</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>367</v>
+        <v>136</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>368</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,16 +2976,16 @@
         <v>62</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>148</v>
+        <v>367</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>151</v>
+        <v>368</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>156</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,16 +2993,16 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>5</v>
+        <v>366</v>
+      </c>
+      <c r="C66" t="s">
+        <v>325</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>110</v>
+        <v>457</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>90</v>
+        <v>459</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,16 +3010,16 @@
         <v>64</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>139</v>
+        <v>440</v>
+      </c>
+      <c r="C67" t="s">
+        <v>325</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>152</v>
+        <v>458</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>157</v>
+        <v>460</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,16 +3027,16 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>3</v>
+        <v>325</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>222</v>
+        <v>151</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2985,16 +3044,16 @@
         <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="C69" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,16 +3061,16 @@
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>270</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3019,16 +3078,16 @@
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>265</v>
+        <v>441</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>267</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3036,16 +3095,16 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3053,16 +3112,16 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3070,16 +3129,16 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>134</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3087,33 +3146,33 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>327</v>
+        <v>266</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>28</v>
+      <c r="B76" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>53</v>
+        <v>272</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3121,33 +3180,33 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>75</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>26</v>
+      <c r="B78" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3155,33 +3214,33 @@
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>227</v>
+        <v>327</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>235</v>
+        <v>328</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>77</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>19</v>
+      <c r="B80" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3189,33 +3248,33 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>79</v>
       </c>
-      <c r="B82" s="11" t="s">
-        <v>166</v>
+      <c r="B82" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3282,16 @@
         <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>288</v>
+        <v>227</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3240,16 +3299,16 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>350</v>
+        <v>19</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>355</v>
+        <v>47</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>356</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3257,16 +3316,16 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3274,16 +3333,16 @@
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3291,16 +3350,16 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>25</v>
+        <v>285</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>50</v>
+        <v>288</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>71</v>
+        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3308,16 +3367,16 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>149</v>
+        <v>350</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>153</v>
+        <v>355</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>158</v>
+        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,16 +3384,16 @@
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3342,16 +3401,16 @@
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3359,16 +3418,16 @@
         <v>88</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3376,16 +3435,16 @@
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>9</v>
+        <v>444</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>41</v>
+        <v>445</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>65</v>
+        <v>446</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3393,16 +3452,16 @@
         <v>90</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3410,16 +3469,16 @@
         <v>91</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3427,16 +3486,16 @@
         <v>92</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>436</v>
+        <v>179</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>325</v>
+        <v>180</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>440</v>
+        <v>193</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>441</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3444,16 +3503,16 @@
         <v>93</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>259</v>
+        <v>187</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>87</v>
+        <v>180</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3461,16 +3520,16 @@
         <v>94</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3478,33 +3537,33 @@
         <v>95</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>87</v>
+        <v>139</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>96</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>56</v>
+      <c r="B99" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>77</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3512,16 +3571,16 @@
         <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>2</v>
+        <v>434</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>3</v>
+        <v>325</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>36</v>
+        <v>438</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>60</v>
+        <v>439</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -3529,16 +3588,16 @@
         <v>98</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -3546,16 +3605,16 @@
         <v>99</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -3563,52 +3622,102 @@
         <v>100</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>101</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>102</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="5">
+        <v>103</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
+        <v>104</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="5">
+        <v>105</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D108" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="5"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="5"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="5"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="5"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="5"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
@@ -3875,7 +3984,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B3:E3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E104">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:E108">
       <sortCondition ref="B3"/>
     </sortState>
   </autoFilter>
@@ -3927,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>146</v>
@@ -3947,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>147</v>
@@ -3967,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>378</v>
+        <v>453</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>146</v>
+        <v>348</v>
       </c>
       <c r="G5" s="5">
         <v>3</v>
@@ -3987,10 +4096,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="5">
         <v>4</v>
@@ -4007,10 +4116,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>374</v>
+        <v>147</v>
       </c>
       <c r="G7" s="5">
         <v>5</v>
@@ -4027,10 +4136,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="G8" s="5">
         <v>6</v>
@@ -4047,10 +4156,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="G9" s="5">
         <v>7</v>
@@ -4067,10 +4176,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>381</v>
+        <v>455</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>146</v>
+        <v>456</v>
       </c>
       <c r="G10" s="5">
         <v>8</v>
@@ -4087,10 +4196,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>147</v>
+        <v>370</v>
       </c>
       <c r="G11" s="5">
         <v>9</v>
@@ -4107,10 +4216,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>203</v>
+        <v>433</v>
       </c>
       <c r="G12" s="5">
         <v>10</v>
@@ -4127,10 +4236,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>347</v>
+        <v>146</v>
       </c>
       <c r="G13" s="5">
         <v>11</v>
@@ -4147,10 +4256,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>435</v>
+        <v>147</v>
       </c>
       <c r="G14" s="5">
         <v>12</v>
@@ -4163,6 +4272,15 @@
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G15" s="5">
         <v>13</v>
       </c>
@@ -4174,6 +4292,15 @@
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G16" s="5">
         <v>14</v>
       </c>
@@ -4185,6 +4312,15 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="G17" s="5">
         <v>15</v>
       </c>
@@ -4196,6 +4332,9 @@
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>16</v>
+      </c>
       <c r="G18" s="5">
         <v>16</v>
       </c>
@@ -4211,7 +4350,7 @@
     </row>
   </sheetData>
   <autoFilter ref="C2:D2" xr:uid="{E2FBB90E-FF6B-41AA-ABD7-678833F5A1B7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:D13">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:D18">
       <sortCondition ref="C2"/>
     </sortState>
   </autoFilter>
@@ -4586,12 +4725,12 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="18" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
@@ -4602,7 +4741,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E3" s="18"/>
     </row>
@@ -4614,8 +4753,8 @@
       <c r="D4" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>387</v>
+      <c r="E4" s="11" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -4627,7 +4766,7 @@
         <v>343</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -4639,19 +4778,19 @@
         <v>343</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>343</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -4663,19 +4802,19 @@
         <v>343</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>343</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -4701,12 +4840,12 @@
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="H2" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
@@ -4716,18 +4855,18 @@
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="13">
+        <v>394</v>
+      </c>
+      <c r="E3" s="12">
         <v>40200</v>
       </c>
       <c r="H3" s="3">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="J3" s="13">
+        <v>394</v>
+      </c>
+      <c r="J3" s="12">
         <v>40200</v>
       </c>
     </row>
@@ -4736,19 +4875,19 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>398</v>
+        <v>395</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>396</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>398</v>
+        <v>395</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
@@ -4756,19 +4895,19 @@
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>400</v>
+        <v>397</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>398</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>400</v>
+        <v>397</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
@@ -4776,18 +4915,18 @@
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="E6" s="13">
+        <v>399</v>
+      </c>
+      <c r="E6" s="12">
         <v>40200</v>
       </c>
       <c r="H6" s="3">
         <v>4</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J6" s="13">
+        <v>399</v>
+      </c>
+      <c r="J6" s="12">
         <v>40200</v>
       </c>
     </row>
@@ -4796,18 +4935,18 @@
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>403</v>
+        <v>400</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H7" s="3">
         <v>5</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J7" s="13" t="b">
+        <v>408</v>
+      </c>
+      <c r="J7" s="12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4816,18 +4955,18 @@
         <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H8" s="3">
         <v>6</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="J8" s="13">
+        <v>409</v>
+      </c>
+      <c r="J8" s="12">
         <v>60</v>
       </c>
     </row>
@@ -4836,18 +4975,18 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="E9" s="13" t="s">
         <v>403</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H9" s="3">
         <v>7</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="J9" s="13">
+        <v>411</v>
+      </c>
+      <c r="J9" s="12">
         <v>60</v>
       </c>
     </row>
@@ -4856,18 +4995,18 @@
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H10" s="3">
         <v>8</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J10" s="13">
+        <v>412</v>
+      </c>
+      <c r="J10" s="12">
         <v>401</v>
       </c>
     </row>
@@ -4876,18 +5015,18 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>403</v>
+        <v>405</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H11" s="3">
         <v>9</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="J11" s="13" t="b">
+        <v>413</v>
+      </c>
+      <c r="J11" s="12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4896,18 +5035,18 @@
         <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E12" s="13">
+        <v>406</v>
+      </c>
+      <c r="E12" s="12">
         <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J12" s="13">
+        <v>414</v>
+      </c>
+      <c r="J12" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4916,19 +5055,19 @@
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="H13" s="3">
         <v>11</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
@@ -4936,18 +5075,18 @@
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E14" s="13" t="b">
+        <v>408</v>
+      </c>
+      <c r="E14" s="12" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="3">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J14" s="13">
+        <v>421</v>
+      </c>
+      <c r="J14" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4956,19 +5095,19 @@
         <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="E15" s="13">
+        <v>409</v>
+      </c>
+      <c r="E15" s="12">
         <v>60</v>
       </c>
       <c r="H15" s="3">
         <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
@@ -4976,18 +5115,18 @@
         <v>14</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E16" s="13">
+        <v>410</v>
+      </c>
+      <c r="E16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="3">
         <v>14</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J16" s="15">
+        <v>424</v>
+      </c>
+      <c r="J16" s="14">
         <v>43572.553746678241</v>
       </c>
     </row>
@@ -4996,18 +5135,18 @@
         <v>15</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E17" s="13">
+        <v>411</v>
+      </c>
+      <c r="E17" s="12">
         <v>60</v>
       </c>
       <c r="H17" s="3">
         <v>15</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J17" s="13">
+        <v>426</v>
+      </c>
+      <c r="J17" s="12">
         <v>4</v>
       </c>
     </row>
@@ -5016,9 +5155,9 @@
         <v>16</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E18" s="13">
+        <v>412</v>
+      </c>
+      <c r="E18" s="12">
         <v>401</v>
       </c>
     </row>
@@ -5027,9 +5166,9 @@
         <v>17</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E19" s="13" t="b">
+        <v>413</v>
+      </c>
+      <c r="E19" s="12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5038,9 +5177,9 @@
         <v>18</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E20" s="13">
+        <v>414</v>
+      </c>
+      <c r="E20" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5049,10 +5188,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>403</v>
+        <v>415</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
@@ -5060,10 +5199,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>403</v>
+        <v>416</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.25">
@@ -5071,10 +5210,10 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>403</v>
+        <v>417</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
@@ -5082,10 +5221,10 @@
         <v>22</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>403</v>
+        <v>418</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.25">
@@ -5093,10 +5232,10 @@
         <v>23</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.25">
@@ -5104,9 +5243,9 @@
         <v>24</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E26" s="13">
+        <v>421</v>
+      </c>
+      <c r="E26" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5115,10 +5254,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.25">
@@ -5126,9 +5265,9 @@
         <v>26</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E28" s="14">
+        <v>424</v>
+      </c>
+      <c r="E28" s="13">
         <v>43572</v>
       </c>
     </row>
@@ -5137,9 +5276,9 @@
         <v>27</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E29" s="15">
+        <v>425</v>
+      </c>
+      <c r="E29" s="14">
         <v>0.55374667824074075</v>
       </c>
     </row>
@@ -5148,10 +5287,10 @@
         <v>28</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>403</v>
+        <v>426</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.25">
@@ -5159,9 +5298,9 @@
         <v>29</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E31" s="13">
+        <v>427</v>
+      </c>
+      <c r="E31" s="12">
         <v>4</v>
       </c>
     </row>
@@ -5170,10 +5309,10 @@
         <v>30</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>403</v>
+        <v>428</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.25">
@@ -5181,10 +5320,10 @@
         <v>31</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>403</v>
+        <v>429</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.25">
@@ -5192,10 +5331,10 @@
         <v>32</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>403</v>
+        <v>430</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.25">
@@ -5203,10 +5342,10 @@
         <v>33</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>403</v>
+        <v>431</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BEFF61-0EB0-438C-A172-2FE4D6625B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E470A-3C52-4631-A250-4E21C90F5075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5E470A-3C52-4631-A250-4E21C90F5075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186745F7-72BD-49D9-83E3-7D2CE0E0DB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Type Sheet" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="461">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1466,7 +1466,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1500,11 +1500,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1545,14 +1582,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1888,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
-  <dimension ref="A2:G131"/>
+  <dimension ref="A2:G132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="6" bestFit="1" customWidth="1"/>
@@ -1903,13 +1949,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -3727,13 +3773,13 @@
       <c r="E109" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
+      <c r="B115" s="17"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="17"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -3825,16 +3871,16 @@
         <v>5</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -3842,16 +3888,16 @@
         <v>6</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3859,10 +3905,10 @@
         <v>7</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>88</v>
@@ -3876,7 +3922,7 @@
         <v>8</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>13</v>
@@ -3888,75 +3934,75 @@
         <v>87</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="16" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
+        <v>9</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
-      <c r="D126" s="16"/>
-      <c r="E126" s="16"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+      <c r="B127" s="20"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="21"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="5">
-        <v>1</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>88</v>
@@ -3967,10 +4013,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>13</v>
@@ -3979,6 +4025,23 @@
         <v>88</v>
       </c>
       <c r="E131" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
+        <v>4</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E132" s="7" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3991,7 +4054,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A127:E127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4374,15 +4437,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
@@ -4724,11 +4787,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="18" t="s">
         <v>384</v>
       </c>
@@ -4839,16 +4902,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="H2" s="17" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="H2" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" s="3">

--- a/Work/Quick Access/Sheets/Type Sheet.xlsx
+++ b/Work/Quick Access/Sheets/Type Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Ganesh Notes\Docs\Work\Quick Access\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186745F7-72BD-49D9-83E3-7D2CE0E0DB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4619F754-432E-461A-9D39-89ECA059AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7A6BE58-0AE6-4559-9D27-1AA220A20AFD}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="471">
   <si>
     <t>TRN_NO</t>
   </si>
@@ -1428,6 +1428,36 @@
   </si>
   <si>
     <t>public decimal PerQty { get; set; }</t>
+  </si>
+  <si>
+    <t>TARGET_PACKING_PRICE</t>
+  </si>
+  <si>
+    <t>TARGET_CHILD_PART_PRICE</t>
+  </si>
+  <si>
+    <t>TARGET_TRANSPORT_PRICE</t>
+  </si>
+  <si>
+    <t>public decimal TARGET_PACKING_PRICE { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal TARGET_CHILD_PART_PRICE { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal TARGET_TRANSPORT_PRICE { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal TargetPackingPrice { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal TargetChildPartPrice { get; set; }</t>
+  </si>
+  <si>
+    <t>public decimal TargetTransportPrice { get; set; }</t>
+  </si>
+  <si>
+    <t>UTYPE_Decimal1:decimal(20, 2)</t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1496,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1487,17 +1517,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1541,7 +1560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1579,17 +1598,11 @@
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1597,8 +1610,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1934,7 +1950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396EB7E8-BA62-40AC-98FB-8FB85DDDAD22}">
-  <dimension ref="A2:G132"/>
+  <dimension ref="A2:G140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="6" bestFit="1" customWidth="1"/>
@@ -1949,13 +1965,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2579,7 +2595,7 @@
       <c r="A39" s="5">
         <v>36</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -3041,7 +3057,7 @@
       <c r="B66" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>325</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -3058,7 +3074,7 @@
       <c r="B67" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>325</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -3075,7 +3091,7 @@
       <c r="B68" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>325</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -3092,7 +3108,7 @@
       <c r="B69" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -3310,7 +3326,7 @@
       <c r="A82" s="5">
         <v>79</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C82" s="3" t="s">
@@ -3449,7 +3465,7 @@
       <c r="B90" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -3766,260 +3782,249 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="5"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
+      <c r="A109" s="5">
+        <v>106</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="5">
+        <v>107</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="5">
+        <v>108</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="5"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="5"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="5"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="5"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="5"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="5"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="5"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="5"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="17"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="B123" s="17"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="17"/>
+      <c r="E123" s="18"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B124" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C124" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="5">
-        <v>1</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
-        <v>2</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
-        <v>3</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
-        <v>4</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
-        <v>5</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="5">
-        <v>6</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="5">
-        <v>7</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="5">
-        <v>8</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
+        <v>2</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D125" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E125" s="7" t="s">
+      <c r="D126" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="B127" s="20"/>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="21"/>
+      <c r="A127" s="5">
+        <v>3</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>59</v>
+      <c r="A128" s="5">
+        <v>4</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>323</v>
+        <v>128</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>87</v>
+        <v>5</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>88</v>
@@ -4030,10 +4035,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>17</v>
+        <v>259</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>13</v>
@@ -4042,6 +4047,117 @@
         <v>88</v>
       </c>
       <c r="E132" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="5">
+        <v>9</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B135" s="17"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="18"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
+        <v>1</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
+        <v>2</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="5">
+        <v>3</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="5">
+        <v>4</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4053,8 +4169,8 @@
   </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A135:E135"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4437,15 +4553,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
@@ -4787,12 +4903,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="18" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20" t="s">
         <v>384</v>
       </c>
     </row>
@@ -4806,7 +4922,7 @@
       <c r="D3" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E3" s="18"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="2:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
@@ -4902,16 +5018,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="H2" s="16" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="H2" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" s="3">
